--- a/06_Yetkili_Kullanıcı_Ürünler/Test_Rail_Test_Caseler/sprint_6___au___pr_test__al__t_rmas_.xlsx
+++ b/06_Yetkili_Kullanıcı_Ürünler/Test_Rail_Test_Caseler/sprint_6___au___pr_test__al__t_rmas_.xlsx
@@ -23,11 +23,41 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="38">
+  <fonts count="44">
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
     </font>
     <font>
       <sz val="11"/>
@@ -234,7 +264,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyBorder="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -345,6 +375,24 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyBorder="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyBorder="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyBorder="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="0" applyBorder="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyBorder="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyBorder="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="0" applyBorder="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -356,7 +404,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:X38"/>
+  <dimension ref="A1:X44"/>
   <sheetData>
     <row r="1" spans="1:24" customHeight="0">
       <c r="A1" s="0" t="inlineStr">
@@ -1217,7 +1265,7 @@
       </c>
       <c r="F16" s="0" t="inlineStr">
         <is>
-          <t>&lt;p margin-left: 0cm;"" data-pasted=""true""&gt;&lt;strong&gt;Testrail test run standart&lt;/strong&gt;&lt;/p&gt;&lt;p margin-left: 0cm;""&gt;&lt;br&gt;&lt;/p&gt;&lt;p margin-left: 0cm;""&gt;Sonuç: Failed&lt;/p&gt;&lt;p margin-left: 0cm;""&gt;&lt;br&gt;&lt;/p&gt;&lt;p margin-left: 0cm;""&gt;Referans Bug ID: BUG-015 [AU-PR]&lt;/p&gt;&lt;p margin-left: 0cm;""&gt;Jira: POW-142&lt;/p&gt;&lt;p margin-left: 0cm;""&gt;&lt;br&gt;&lt;/p&gt;&lt;p margin-left: 0cm;""&gt;Not:&lt;/p&gt;&lt;p margin-left: 0cm;""&gt;Ürün miktarı alanında geçersiz veri girildiğinde hata bildirim modalı görüntülenmiyor&lt;/p&gt;</t>
+          <t>&lt;p margin: 12px 0px 12px 0cm; padding: 0px; border: 0px; font-style: normal; font-variant-ligatures: normal; font-variant-caps: normal; font-variant-numeric: inherit; font-variant-east-asian: inherit; font-variant-alternates: inherit; font-variant-position: inherit; font-variant-emoji: inherit; font-weight: 400; font-stretch: inherit; font-size: 14px; line-height: 19.6px; font-family: Arial, -apple-system, BlinkMacSystemFont, system-ui, sans-serif; font-optical-sizing: inherit; font-size-adjust: inherit; font-kerning: inherit; font-feature-settings: inherit; font-variation-settings: inherit; font-language-override: inherit; vertical-align: baseline; x: 140%; color: rgb(32, 32, 32); letter-spacing: normal; orphans: 2; text-align: start; text-indent: 0px; text-transform: none; widows: 2; word-spacing: 0px; -webkit-text-stroke-width: 0px; white-space: normal; background-color: rgb(255, 255, 255); text-decoration-thickness: initial; text-decoration-style: initial; text-decoration-color: initial;"" data-pasted=""true""&gt;Sonuç: Failed&lt;/p&gt;&lt;p margin: 12px 0px 12px 0cm; padding: 0px; border: 0px; font-style: normal; font-variant-ligatures: normal; font-variant-caps: normal; font-variant-numeric: inherit; font-variant-east-asian: inherit; font-variant-alternates: inherit; font-variant-position: inherit; font-variant-emoji: inherit; font-weight: 400; font-stretch: inherit; font-size: 14px; line-height: 19.6px; font-family: Arial, -apple-system, BlinkMacSystemFont, system-ui, sans-serif; font-optical-sizing: inherit; font-size-adjust: inherit; font-kerning: inherit; font-feature-settings: inherit; font-variation-settings: inherit; font-language-override: inherit; vertical-align: baseline; x: 140%; color: rgb(32, 32, 32); letter-spacing: normal; orphans: 2; text-align: start; text-indent: 0px; text-transform: none; widows: 2; word-spacing: 0px; -webkit-text-stroke-width: 0px; white-space: normal; background-color: rgb(255, 255, 255); text-decoration-thickness: initial; text-decoration-style: initial; text-decoration-color: initial;""&gt;&lt;br margin-bottom: 0px;""&gt;&lt;/p&gt;&lt;p margin: 12px 0px 12px 0cm; padding: 0px; border: 0px; font-style: normal; font-variant-ligatures: normal; font-variant-caps: normal; font-variant-numeric: inherit; font-variant-east-asian: inherit; font-variant-alternates: inherit; font-variant-position: inherit; font-variant-emoji: inherit; font-weight: 400; font-stretch: inherit; font-size: 14px; line-height: 19.6px; font-family: Arial, -apple-system, BlinkMacSystemFont, system-ui, sans-serif; font-optical-sizing: inherit; font-size-adjust: inherit; font-kerning: inherit; font-feature-settings: inherit; font-variation-settings: inherit; font-language-override: inherit; vertical-align: baseline; x: 140%; color: rgb(32, 32, 32); letter-spacing: normal; orphans: 2; text-align: start; text-indent: 0px; text-transform: none; widows: 2; word-spacing: 0px; -webkit-text-stroke-width: 0px; white-space: normal; background-color: rgb(255, 255, 255); text-decoration-thickness: initial; text-decoration-style: initial; text-decoration-color: initial;""&gt;Referans Bug ID: BUG-015 [AU-PR]&lt;/p&gt;&lt;p margin: 12px 0px 12px 0cm; padding: 0px; border: 0px; font-style: normal; font-variant-ligatures: normal; font-variant-caps: normal; font-variant-numeric: inherit; font-variant-east-asian: inherit; font-variant-alternates: inherit; font-variant-position: inherit; font-variant-emoji: inherit; font-weight: 400; font-stretch: inherit; font-size: 14px; line-height: 19.6px; font-family: Arial, -apple-system, BlinkMacSystemFont, system-ui, sans-serif; font-optical-sizing: inherit; font-size-adjust: inherit; font-kerning: inherit; font-feature-settings: inherit; font-variation-settings: inherit; font-language-override: inherit; vertical-align: baseline; x: 140%; color: rgb(32, 32, 32); letter-spacing: normal; orphans: 2; text-align: start; text-indent: 0px; text-transform: none; widows: 2; word-spacing: 0px; -webkit-text-stroke-width: 0px; white-space: normal; background-color: rgb(255, 255, 255); text-decoration-thickness: initial; text-decoration-style: initial; text-decoration-color: initial;""&gt;Jira: POW-143&lt;/p&gt;</t>
         </is>
       </c>
       <c r="I16" s="0" t="inlineStr">
@@ -1437,60 +1485,305 @@
     <row r="22" spans="1:24" customHeight="0">
       <c r="A22" s="0" t="inlineStr">
         <is>
+          <t>T146</t>
+        </is>
+      </c>
+      <c r="B22" s="0" t="inlineStr">
+        <is>
+          <t>TC - 027 [AU - PR] - Tüketilen ürün miktar alanı</t>
+        </is>
+      </c>
+      <c r="C22" s="0" t="inlineStr">
+        <is>
+          <t>Beril Ovayurt</t>
+        </is>
+      </c>
+      <c r="D22" s="0" t="inlineStr">
+        <is>
+          <t>Beril Ovayurt</t>
+        </is>
+      </c>
+      <c r="E22" s="0" t="inlineStr">
+        <is>
+          <t>C82</t>
+        </is>
+      </c>
+      <c r="F22" s="0" t="inlineStr">
+        <is>
+          <t>&lt;p margin-left: 0cm;"" data-pasted=""true""&gt;&lt;strong&gt;Testrail test run standart&lt;/strong&gt;&lt;/p&gt;&lt;p margin-left: 0cm;""&gt;&lt;br&gt;&lt;/p&gt;&lt;p margin-left: 0cm;""&gt;Sonuç: Failed&lt;/p&gt;&lt;p margin-left: 0cm;""&gt;&lt;br&gt;&lt;/p&gt;&lt;p margin-left: 0cm;""&gt;Referans Bug ID: BUG-015 [AU-PR]&lt;/p&gt;&lt;p margin-left: 0cm;""&gt;Jira: POW-142&lt;/p&gt;&lt;p margin-left: 0cm;""&gt;&lt;br&gt;&lt;/p&gt;&lt;p margin-left: 0cm;""&gt;Not:&lt;/p&gt;&lt;p margin-left: 0cm;""&gt;Ürün miktarı alanında geçersiz veri girildiğinde hata bildirim modalı görüntülenmiyor&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="I22" s="0" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J22" s="0" t="inlineStr">
+        <is>
+          <t>Sprint 6 - AU - PR Test Çalıştırması</t>
+        </is>
+      </c>
+      <c r="L22" s="0" t="inlineStr">
+        <is>
+          <t>R17</t>
+        </is>
+      </c>
+      <c r="M22" s="0" t="inlineStr">
+        <is>
+          <t>06 - Yetkili Kullanıcı - Products (AU - PR)</t>
+        </is>
+      </c>
+      <c r="N22" s="0" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="P22" s="21" t="inlineStr">
+        <is>
+          <t>Step Description:
+Sadece ürün miktarı alanı boş Add to Diary butonu tıklanır
+Expected Result:
+Bir hata bildirim modal penceresi görüntülenir (1), form gönderilmez (2)</t>
+        </is>
+      </c>
+      <c r="Q22" s="0" t="inlineStr">
+        <is>
+          <t>Geçersiz ürün miktarı girildiğinde Add to Diary işlemi gerçekleştirilmemekte, ancak hata bildirim modalı görüntülenmemektedir.</t>
+        </is>
+      </c>
+      <c r="S22" s="0" t="inlineStr">
+        <is>
+          <t>Bir hata bildirim modal penceresi görüntülenir (1), form gönderilmez (2)</t>
+        </is>
+      </c>
+      <c r="T22" s="0" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="U22" s="0" t="inlineStr">
+        <is>
+          <t>Sadece ürün miktarı alanı boş Add to Diary butonu tıklanır</t>
+        </is>
+      </c>
+      <c r="V22" s="0" t="inlineStr">
+        <is>
+          <t>Beril Ovayurt</t>
+        </is>
+      </c>
+      <c r="W22" s="0" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="X22" s="0" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" spans="1:24" customHeight="0">
+      <c r="P23" s="22" t="inlineStr">
+        <is>
+          <t>
+Step Description:
+&lt;p&gt;Ürün miktarı alanına harf/özel karakter girip Add to Diary butonu tıklanır&lt;/p&gt;
+Expected Result:
+&lt;p&gt;Bir hata bildirim modal penceresi görüntülenir (1), form gönderilmez (2)&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="Q23" s="0" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Geçersiz ürün miktarı girildiğinde Add to Diary işlemi gerçekleştirilmemekte, ancak hata bildirim modalı görüntülenmemektedir.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="S23" s="0" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Bir hata bildirim modal penceresi görüntülenir (1), form gönderilmez (2)&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="T23" s="0" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="U23" s="0" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Ürün miktarı alanına harf/özel karakter girip Add to Diary butonu tıklanır&lt;/p&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" spans="1:24" customHeight="0">
+      <c r="P24" s="23" t="inlineStr">
+        <is>
+          <t>
+Step Description:
+&lt;p&gt;Ürün miktarı alanına 0 girip Add to Diary butonu tıklanır&lt;/p&gt;
+Expected Result:
+&lt;p&gt;Bir hata bildirim modal penceresi görüntülenir (1), form gönderilmez (2)&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="Q24" s="0" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Geçersiz ürün miktarı girildiğinde Add to Diary işlemi gerçekleştirilmemekte, ancak hata bildirim modalı görüntülenmemektedir.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="S24" s="0" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Bir hata bildirim modal penceresi görüntülenir (1), form gönderilmez (2)&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="T24" s="0" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="U24" s="0" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Ürün miktarı alanına 0 girip Add to Diary butonu tıklanır&lt;/p&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" spans="1:24" customHeight="0">
+      <c r="P25" s="24" t="inlineStr">
+        <is>
+          <t>
+Step Description:
+&lt;p&gt;Ürün miktarı alanına - 5 girip Add to Diary butonu tıklanır&lt;/p&gt;
+Expected Result:
+&lt;p&gt;Bir hata bildirim modal penceresi görüntülenir (1), form gönderilmez (2)&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="Q25" s="0" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Geçersiz ürün miktarı girildiğinde Add to Diary işlemi gerçekleştirilmemekte, ancak hata bildirim modalı görüntülenmemektedir.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="S25" s="0" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Bir hata bildirim modal penceresi görüntülenir (1), form gönderilmez (2)&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="T25" s="0" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="U25" s="0" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Ürün miktarı alanına - 5 girip Add to Diary butonu tıklanır&lt;/p&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" spans="1:24" customHeight="0">
+      <c r="P26" s="25" t="inlineStr">
+        <is>
+          <t>
+Step Description:
+&lt;p&gt;Ürün miktarı alanına 1 girip Add to Diary butonu tıklanır&lt;/p&gt;
+Expected Result:
+&lt;p&gt;Bir onay bildirim modal penceresi görüntülenir (1), Ürünün tüketilenler listesine eklendiği görüntülenir (2)&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="S26" s="0" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Bir onay bildirim modal penceresi görüntülenir (1), Ürünün tüketilenler listesine eklendiği görüntülenir (2)&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="T26" s="0" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="U26" s="0" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Ürün miktarı alanına 1 girip Add to Diary butonu tıklanır&lt;/p&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" spans="1:24" customHeight="0">
+      <c r="P27" s="26" t="inlineStr">
+        <is>
+          <t>
+Step Description:
+&lt;p&gt;Ürün miktarı alanına 250 girip Add to Diary butonu tıklanır&lt;/p&gt;
+Expected Result:
+&lt;p&gt;Bir onay bildirim modal penceresi görüntülenir (1), Ürünün tüketilenler listesine eklendiği görüntülenir (2)&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="S27" s="0" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Bir onay bildirim modal penceresi görüntülenir (1), Ürünün tüketilenler listesine eklendiği görüntülenir (2)&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="T27" s="0" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="U27" s="0" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Ürün miktarı alanına 250 girip Add to Diary butonu tıklanır&lt;/p&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" spans="1:24" customHeight="0">
+      <c r="A28" s="0" t="inlineStr">
+        <is>
           <t>T147</t>
         </is>
       </c>
-      <c r="B22" s="0" t="inlineStr">
+      <c r="B28" s="0" t="inlineStr">
         <is>
           <t>TC - 028 [AU - PR] - Ürüne Göre Kalori Miktarı Hesabı</t>
         </is>
       </c>
-      <c r="C22" s="0" t="inlineStr">
-        <is>
-          <t>Beril Ovayurt</t>
-        </is>
-      </c>
-      <c r="D22" s="0" t="inlineStr">
-        <is>
-          <t>Beril Ovayurt</t>
-        </is>
-      </c>
-      <c r="E22" s="0" t="inlineStr">
+      <c r="C28" s="0" t="inlineStr">
+        <is>
+          <t>Beril Ovayurt</t>
+        </is>
+      </c>
+      <c r="D28" s="0" t="inlineStr">
+        <is>
+          <t>Beril Ovayurt</t>
+        </is>
+      </c>
+      <c r="E28" s="0" t="inlineStr">
         <is>
           <t>C83</t>
         </is>
       </c>
-      <c r="F22" s="0" t="inlineStr">
+      <c r="F28" s="0" t="inlineStr">
         <is>
           <t>&lt;p margin-left:0cm;"" data-pasted=""true""&gt;Sonuç: Passed&lt;/p&gt;&lt;p margin-left:0cm;""&gt;&lt;br&gt;&lt;/p&gt;&lt;p margin-left:0cm;""&gt;Beklenen sonuç elde edildi.&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="I22" s="0" t="inlineStr">
+      <c r="I28" s="0" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="J22" s="0" t="inlineStr">
+      <c r="J28" s="0" t="inlineStr">
         <is>
           <t>Sprint 6 - AU - PR Test Çalıştırması</t>
         </is>
       </c>
-      <c r="L22" s="0" t="inlineStr">
+      <c r="L28" s="0" t="inlineStr">
         <is>
           <t>R17</t>
         </is>
       </c>
-      <c r="M22" s="0" t="inlineStr">
+      <c r="M28" s="0" t="inlineStr">
         <is>
           <t>06 - Yetkili Kullanıcı - Products (AU - PR)</t>
         </is>
       </c>
-      <c r="N22" s="0" t="inlineStr">
-        <is>
-          <t>Passed</t>
-        </is>
-      </c>
-      <c r="P22" s="21" t="inlineStr">
+      <c r="N28" s="0" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="P28" s="27" t="inlineStr">
         <is>
           <t>Step Description:
 Modalda ürün miktarı 50 g girilip Add to Diary butonu tıklanır
@@ -1498,39 +1791,39 @@
 Kalori değeri (50 × 200) / 100 = 100 kcal olarak görüntülenir</t>
         </is>
       </c>
-      <c r="S22" s="0" t="inlineStr">
+      <c r="S28" s="0" t="inlineStr">
         <is>
           <t>Kalori değeri (50 × 200) / 100 = 100 kcal olarak görüntülenir</t>
         </is>
       </c>
-      <c r="T22" s="0" t="inlineStr">
-        <is>
-          <t>Passed</t>
-        </is>
-      </c>
-      <c r="U22" s="0" t="inlineStr">
+      <c r="T28" s="0" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="U28" s="0" t="inlineStr">
         <is>
           <t>Modalda ürün miktarı 50 g girilip Add to Diary butonu tıklanır</t>
         </is>
       </c>
-      <c r="V22" s="0" t="inlineStr">
-        <is>
-          <t>Beril Ovayurt</t>
-        </is>
-      </c>
-      <c r="W22" s="0" t="inlineStr">
+      <c r="V28" s="0" t="inlineStr">
+        <is>
+          <t>Beril Ovayurt</t>
+        </is>
+      </c>
+      <c r="W28" s="0" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="X22" s="0" t="inlineStr">
+      <c r="X28" s="0" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
     </row>
-    <row r="23" spans="1:24" customHeight="0">
-      <c r="P23" s="22" t="inlineStr">
+    <row r="29" spans="1:24" customHeight="0">
+      <c r="P29" s="28" t="inlineStr">
         <is>
           <t>
 Step Description:
@@ -1539,24 +1832,24 @@
 &lt;p&gt;Request üzerinden ve verilen formülle hesaplanan değerlerin eşit olduğu görülür&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="S23" s="0" t="inlineStr">
+      <c r="S29" s="0" t="inlineStr">
         <is>
           <t>&lt;p&gt;Request üzerinden ve verilen formülle hesaplanan değerlerin eşit olduğu görülür&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="T23" s="0" t="inlineStr">
-        <is>
-          <t>Passed</t>
-        </is>
-      </c>
-      <c r="U23" s="0" t="inlineStr">
+      <c r="T29" s="0" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="U29" s="0" t="inlineStr">
         <is>
           <t>&lt;p&gt;Backend'e giden request gözlenir&lt;/p&gt;</t>
         </is>
       </c>
     </row>
-    <row r="24" spans="1:24" customHeight="0">
-      <c r="P24" s="23" t="inlineStr">
+    <row r="30" spans="1:24" customHeight="0">
+      <c r="P30" s="29" t="inlineStr">
         <is>
           <t>
 Step Description:
@@ -1565,24 +1858,24 @@
 &lt;p&gt;Kalori değeri (100 × 200) / 100 = 200 kcal olarak görüntülenir&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="S24" s="0" t="inlineStr">
+      <c r="S30" s="0" t="inlineStr">
         <is>
           <t>&lt;p&gt;Kalori değeri (100 × 200) / 100 = 200 kcal olarak görüntülenir&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="T24" s="0" t="inlineStr">
-        <is>
-          <t>Passed</t>
-        </is>
-      </c>
-      <c r="U24" s="0" t="inlineStr">
+      <c r="T30" s="0" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="U30" s="0" t="inlineStr">
         <is>
           <t>&lt;p&gt;Modalda ürün miktarı 100 g girilip Add to Diary butonu tıklanır&lt;/p&gt;</t>
         </is>
       </c>
     </row>
-    <row r="25" spans="1:24" customHeight="0">
-      <c r="P25" s="24" t="inlineStr">
+    <row r="31" spans="1:24" customHeight="0">
+      <c r="P31" s="30" t="inlineStr">
         <is>
           <t>
 Step Description:
@@ -1591,24 +1884,24 @@
 &lt;p&gt;Kalori değeri (250 × 200) / 100 = 500 kcal olarak görüntülenir&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="S25" s="0" t="inlineStr">
+      <c r="S31" s="0" t="inlineStr">
         <is>
           <t>&lt;p&gt;Kalori değeri (250 × 200) / 100 = 500 kcal olarak görüntülenir&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="T25" s="0" t="inlineStr">
-        <is>
-          <t>Passed</t>
-        </is>
-      </c>
-      <c r="U25" s="0" t="inlineStr">
+      <c r="T31" s="0" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="U31" s="0" t="inlineStr">
         <is>
           <t>&lt;p&gt;Modalda ürün miktarı 250 g girilip Add to Diary butonu tıklanır&lt;/p&gt;</t>
         </is>
       </c>
     </row>
-    <row r="26" spans="1:24" customHeight="0">
-      <c r="P26" s="25" t="inlineStr">
+    <row r="32" spans="1:24" customHeight="0">
+      <c r="P32" s="31" t="inlineStr">
         <is>
           <t>
 Step Description:
@@ -1617,79 +1910,79 @@
 &lt;p&gt;Kalori değeri (1 × 200) / 100 = 2 kcal olarak görüntülenir&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="S26" s="0" t="inlineStr">
+      <c r="S32" s="0" t="inlineStr">
         <is>
           <t>&lt;p&gt;Kalori değeri (1 × 200) / 100 = 2 kcal olarak görüntülenir&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="T26" s="0" t="inlineStr">
-        <is>
-          <t>Passed</t>
-        </is>
-      </c>
-      <c r="U26" s="0" t="inlineStr">
+      <c r="T32" s="0" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="U32" s="0" t="inlineStr">
         <is>
           <t>&lt;p&gt;Modalda ürün miktarı 1 g girilip Add to Diary butonu tıklanır&lt;/p&gt;</t>
         </is>
       </c>
     </row>
-    <row r="27" spans="1:24" customHeight="0">
-      <c r="A27" s="0" t="inlineStr">
+    <row r="33" spans="1:24" customHeight="0">
+      <c r="A33" s="0" t="inlineStr">
         <is>
           <t>T148</t>
         </is>
       </c>
-      <c r="B27" s="0" t="inlineStr">
+      <c r="B33" s="0" t="inlineStr">
         <is>
           <t>TC - 029 [AU - PR] - Add to Diary Butonu - Backend</t>
         </is>
       </c>
-      <c r="C27" s="0" t="inlineStr">
-        <is>
-          <t>Beril Ovayurt</t>
-        </is>
-      </c>
-      <c r="D27" s="0" t="inlineStr">
-        <is>
-          <t>Beril Ovayurt</t>
-        </is>
-      </c>
-      <c r="E27" s="0" t="inlineStr">
+      <c r="C33" s="0" t="inlineStr">
+        <is>
+          <t>Beril Ovayurt</t>
+        </is>
+      </c>
+      <c r="D33" s="0" t="inlineStr">
+        <is>
+          <t>Beril Ovayurt</t>
+        </is>
+      </c>
+      <c r="E33" s="0" t="inlineStr">
         <is>
           <t>C84</t>
         </is>
       </c>
-      <c r="F27" s="0" t="inlineStr">
+      <c r="F33" s="0" t="inlineStr">
         <is>
           <t>&lt;p margin-left:0cm;"" data-pasted=""true""&gt;Sonuç: Passed&lt;/p&gt;&lt;p margin-left:0cm;""&gt;&lt;br&gt;&lt;/p&gt;&lt;p margin-left:0cm;""&gt;Beklenen sonuç elde edildi.&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="I27" s="0" t="inlineStr">
+      <c r="I33" s="0" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="J27" s="0" t="inlineStr">
+      <c r="J33" s="0" t="inlineStr">
         <is>
           <t>Sprint 6 - AU - PR Test Çalıştırması</t>
         </is>
       </c>
-      <c r="L27" s="0" t="inlineStr">
+      <c r="L33" s="0" t="inlineStr">
         <is>
           <t>R17</t>
         </is>
       </c>
-      <c r="M27" s="0" t="inlineStr">
+      <c r="M33" s="0" t="inlineStr">
         <is>
           <t>06 - Yetkili Kullanıcı - Products (AU - PR)</t>
         </is>
       </c>
-      <c r="N27" s="0" t="inlineStr">
-        <is>
-          <t>Passed</t>
-        </is>
-      </c>
-      <c r="P27" s="26" t="inlineStr">
+      <c r="N33" s="0" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="P33" s="32" t="inlineStr">
         <is>
           <t>Step Description:
 Bir ürün bloğundaki Add to diary butonuna tıklanır
@@ -1697,39 +1990,39 @@
 Backendde request görüntülenir</t>
         </is>
       </c>
-      <c r="S27" s="0" t="inlineStr">
+      <c r="S33" s="0" t="inlineStr">
         <is>
           <t>Backendde request görüntülenir</t>
         </is>
       </c>
-      <c r="T27" s="0" t="inlineStr">
-        <is>
-          <t>Passed</t>
-        </is>
-      </c>
-      <c r="U27" s="0" t="inlineStr">
+      <c r="T33" s="0" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="U33" s="0" t="inlineStr">
         <is>
           <t>Bir ürün bloğundaki Add to diary butonuna tıklanır</t>
         </is>
       </c>
-      <c r="V27" s="0" t="inlineStr">
-        <is>
-          <t>Beril Ovayurt</t>
-        </is>
-      </c>
-      <c r="W27" s="0" t="inlineStr">
+      <c r="V33" s="0" t="inlineStr">
+        <is>
+          <t>Beril Ovayurt</t>
+        </is>
+      </c>
+      <c r="W33" s="0" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="X27" s="0" t="inlineStr">
+      <c r="X33" s="0" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
     </row>
-    <row r="28" spans="1:24" customHeight="0">
-      <c r="P28" s="27" t="inlineStr">
+    <row r="34" spans="1:24" customHeight="0">
+      <c r="P34" s="33" t="inlineStr">
         <is>
           <t>
 Step Description:
@@ -1738,79 +2031,79 @@
 &lt;p&gt;Request'in doğru endpoint'e gönderildiği doğrulanır.&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="S28" s="0" t="inlineStr">
+      <c r="S34" s="0" t="inlineStr">
         <is>
           <t>&lt;p&gt;Request'in doğru endpoint'e gönderildiği doğrulanır.&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="T28" s="0" t="inlineStr">
-        <is>
-          <t>Passed</t>
-        </is>
-      </c>
-      <c r="U28" s="0" t="inlineStr">
+      <c r="T34" s="0" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="U34" s="0" t="inlineStr">
         <is>
           <t>&lt;p&gt;Backend'deki request incelenir&lt;/p&gt;</t>
         </is>
       </c>
     </row>
-    <row r="29" spans="1:24" customHeight="0">
-      <c r="A29" s="0" t="inlineStr">
+    <row r="35" spans="1:24" customHeight="0">
+      <c r="A35" s="0" t="inlineStr">
         <is>
           <t>T149</t>
         </is>
       </c>
-      <c r="B29" s="0" t="inlineStr">
+      <c r="B35" s="0" t="inlineStr">
         <is>
           <t>TC - 030 [AU - PR] - Modal Pencere - Cancel ve Çarpı İşareti Davranışı</t>
         </is>
       </c>
-      <c r="C29" s="0" t="inlineStr">
-        <is>
-          <t>Beril Ovayurt</t>
-        </is>
-      </c>
-      <c r="D29" s="0" t="inlineStr">
-        <is>
-          <t>Beril Ovayurt</t>
-        </is>
-      </c>
-      <c r="E29" s="0" t="inlineStr">
+      <c r="C35" s="0" t="inlineStr">
+        <is>
+          <t>Beril Ovayurt</t>
+        </is>
+      </c>
+      <c r="D35" s="0" t="inlineStr">
+        <is>
+          <t>Beril Ovayurt</t>
+        </is>
+      </c>
+      <c r="E35" s="0" t="inlineStr">
         <is>
           <t>C85</t>
         </is>
       </c>
-      <c r="F29" s="0" t="inlineStr">
+      <c r="F35" s="0" t="inlineStr">
         <is>
           <t>&lt;p margin-left:0cm;"" data-pasted=""true""&gt;Sonuç: Passed&lt;/p&gt;&lt;p margin-left:0cm;""&gt;&lt;br&gt;&lt;/p&gt;&lt;p margin-left:0cm;""&gt;Beklenen sonuç elde edildi.&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="I29" s="0" t="inlineStr">
+      <c r="I35" s="0" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="J29" s="0" t="inlineStr">
+      <c r="J35" s="0" t="inlineStr">
         <is>
           <t>Sprint 6 - AU - PR Test Çalıştırması</t>
         </is>
       </c>
-      <c r="L29" s="0" t="inlineStr">
+      <c r="L35" s="0" t="inlineStr">
         <is>
           <t>R17</t>
         </is>
       </c>
-      <c r="M29" s="0" t="inlineStr">
+      <c r="M35" s="0" t="inlineStr">
         <is>
           <t>06 - Yetkili Kullanıcı - Products (AU - PR)</t>
         </is>
       </c>
-      <c r="N29" s="0" t="inlineStr">
-        <is>
-          <t>Passed</t>
-        </is>
-      </c>
-      <c r="P29" s="28" t="inlineStr">
+      <c r="N35" s="0" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="P35" s="34" t="inlineStr">
         <is>
           <t>Step Description:
 Modal penceresinde Cancel butonu tıklanır
@@ -1818,39 +2111,39 @@
 Modal pencere kapanır, kullanıcı mevcut sayfada kalır</t>
         </is>
       </c>
-      <c r="S29" s="0" t="inlineStr">
+      <c r="S35" s="0" t="inlineStr">
         <is>
           <t>Modal pencere kapanır, kullanıcı mevcut sayfada kalır</t>
         </is>
       </c>
-      <c r="T29" s="0" t="inlineStr">
-        <is>
-          <t>Passed</t>
-        </is>
-      </c>
-      <c r="U29" s="0" t="inlineStr">
+      <c r="T35" s="0" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="U35" s="0" t="inlineStr">
         <is>
           <t>Modal penceresinde Cancel butonu tıklanır</t>
         </is>
       </c>
-      <c r="V29" s="0" t="inlineStr">
-        <is>
-          <t>Beril Ovayurt</t>
-        </is>
-      </c>
-      <c r="W29" s="0" t="inlineStr">
+      <c r="V35" s="0" t="inlineStr">
+        <is>
+          <t>Beril Ovayurt</t>
+        </is>
+      </c>
+      <c r="W35" s="0" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="X29" s="0" t="inlineStr">
+      <c r="X35" s="0" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
     </row>
-    <row r="30" spans="1:24" customHeight="0">
-      <c r="P30" s="29" t="inlineStr">
+    <row r="36" spans="1:24" customHeight="0">
+      <c r="P36" s="35" t="inlineStr">
         <is>
           <t>
 Step Description:
@@ -1859,24 +2152,24 @@
 &lt;p&gt;Ürün için yeni kayıt bulunmaz, tüketilenler listesi değişmez&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="S30" s="0" t="inlineStr">
+      <c r="S36" s="0" t="inlineStr">
         <is>
           <t>&lt;p&gt;Ürün için yeni kayıt bulunmaz, tüketilenler listesi değişmez&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="T30" s="0" t="inlineStr">
-        <is>
-          <t>Passed</t>
-        </is>
-      </c>
-      <c r="U30" s="0" t="inlineStr">
+      <c r="T36" s="0" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="U36" s="0" t="inlineStr">
         <is>
           <t>&lt;p&gt;İşlemden sonra ilgili ürünün backend kaydı kontrol edilir&lt;/p&gt;</t>
         </is>
       </c>
     </row>
-    <row r="31" spans="1:24" customHeight="0">
-      <c r="P31" s="30" t="inlineStr">
+    <row r="37" spans="1:24" customHeight="0">
+      <c r="P37" s="36" t="inlineStr">
         <is>
           <t>
 Step Description:
@@ -1885,24 +2178,24 @@
 &lt;p&gt;Modalda çarpı işareti görünür olur&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="S31" s="0" t="inlineStr">
+      <c r="S37" s="0" t="inlineStr">
         <is>
           <t>&lt;p&gt;Modalda çarpı işareti görünür olur&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="T31" s="0" t="inlineStr">
-        <is>
-          <t>Passed</t>
-        </is>
-      </c>
-      <c r="U31" s="0" t="inlineStr">
+      <c r="T37" s="0" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="U37" s="0" t="inlineStr">
         <is>
           <t>&lt;p&gt;Modal yeniden açılır, ürün miktarı alanına geçerli bir değer girilir.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
-    <row r="32" spans="1:24" customHeight="0">
-      <c r="P32" s="31" t="inlineStr">
+    <row r="38" spans="1:24" customHeight="0">
+      <c r="P38" s="37" t="inlineStr">
         <is>
           <t>
 Step Description:
@@ -1911,24 +2204,24 @@
 &lt;p&gt;Modal pencere kapanır, kullanıcı mevcut sayfada kalır&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="S32" s="0" t="inlineStr">
+      <c r="S38" s="0" t="inlineStr">
         <is>
           <t>&lt;p&gt;Modal pencere kapanır, kullanıcı mevcut sayfada kalır&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="T32" s="0" t="inlineStr">
-        <is>
-          <t>Passed</t>
-        </is>
-      </c>
-      <c r="U32" s="0" t="inlineStr">
+      <c r="T38" s="0" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="U38" s="0" t="inlineStr">
         <is>
           <t>&lt;p&gt;Çarpı işaretine tıklanır&lt;/p&gt;</t>
         </is>
       </c>
     </row>
-    <row r="33" spans="1:24" customHeight="0">
-      <c r="P33" s="32" t="inlineStr">
+    <row r="39" spans="1:24" customHeight="0">
+      <c r="P39" s="38" t="inlineStr">
         <is>
           <t>
 Step Description:
@@ -1937,79 +2230,79 @@
 &lt;p&gt;Bilgiler Backendde bulunmaz, tüketilenler listesi değişmez&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="S33" s="0" t="inlineStr">
+      <c r="S39" s="0" t="inlineStr">
         <is>
           <t>&lt;p&gt;Bilgiler Backendde bulunmaz, tüketilenler listesi değişmez&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="T33" s="0" t="inlineStr">
-        <is>
-          <t>Passed</t>
-        </is>
-      </c>
-      <c r="U33" s="0" t="inlineStr">
+      <c r="T39" s="0" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="U39" s="0" t="inlineStr">
         <is>
           <t>&lt;p&gt;İşlemden sonra ilgili ürünün backend kaydı kontrol edilir&lt;/p&gt;</t>
         </is>
       </c>
     </row>
-    <row r="34" spans="1:24" customHeight="0">
-      <c r="A34" s="0" t="inlineStr">
+    <row r="40" spans="1:24" customHeight="0">
+      <c r="A40" s="0" t="inlineStr">
         <is>
           <t>T150</t>
         </is>
       </c>
-      <c r="B34" s="0" t="inlineStr">
+      <c r="B40" s="0" t="inlineStr">
         <is>
           <t>TC - 031 [AU - PR] - Modal Pencerede Add to Diary Davranışı</t>
         </is>
       </c>
-      <c r="C34" s="0" t="inlineStr">
-        <is>
-          <t>Beril Ovayurt</t>
-        </is>
-      </c>
-      <c r="D34" s="0" t="inlineStr">
-        <is>
-          <t>Beril Ovayurt</t>
-        </is>
-      </c>
-      <c r="E34" s="0" t="inlineStr">
+      <c r="C40" s="0" t="inlineStr">
+        <is>
+          <t>Beril Ovayurt</t>
+        </is>
+      </c>
+      <c r="D40" s="0" t="inlineStr">
+        <is>
+          <t>Beril Ovayurt</t>
+        </is>
+      </c>
+      <c r="E40" s="0" t="inlineStr">
         <is>
           <t>C86</t>
         </is>
       </c>
-      <c r="F34" s="0" t="inlineStr">
+      <c r="F40" s="0" t="inlineStr">
         <is>
           <t>&lt;p margin-left:0cm;"" data-pasted=""true""&gt;Sonuç: Passed&lt;/p&gt;&lt;p margin-left:0cm;""&gt;&lt;br&gt;&lt;/p&gt;&lt;p margin-left:0cm;""&gt;Beklenen sonuç elde edildi.&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="I34" s="0" t="inlineStr">
+      <c r="I40" s="0" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="J34" s="0" t="inlineStr">
+      <c r="J40" s="0" t="inlineStr">
         <is>
           <t>Sprint 6 - AU - PR Test Çalıştırması</t>
         </is>
       </c>
-      <c r="L34" s="0" t="inlineStr">
+      <c r="L40" s="0" t="inlineStr">
         <is>
           <t>R17</t>
         </is>
       </c>
-      <c r="M34" s="0" t="inlineStr">
+      <c r="M40" s="0" t="inlineStr">
         <is>
           <t>06 - Yetkili Kullanıcı - Products (AU - PR)</t>
         </is>
       </c>
-      <c r="N34" s="0" t="inlineStr">
-        <is>
-          <t>Passed</t>
-        </is>
-      </c>
-      <c r="P34" s="33" t="inlineStr">
+      <c r="N40" s="0" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="P40" s="39" t="inlineStr">
         <is>
           <t>Step Description:
 Modala geçerli bir veri girilerek Add to dairy butonu tıklanır
@@ -2017,39 +2310,39 @@
 Başarı bildirimi görüntülenir (1), modal kapanır (2)</t>
         </is>
       </c>
-      <c r="S34" s="0" t="inlineStr">
+      <c r="S40" s="0" t="inlineStr">
         <is>
           <t>Başarı bildirimi görüntülenir (1), modal kapanır (2)</t>
         </is>
       </c>
-      <c r="T34" s="0" t="inlineStr">
-        <is>
-          <t>Passed</t>
-        </is>
-      </c>
-      <c r="U34" s="0" t="inlineStr">
+      <c r="T40" s="0" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="U40" s="0" t="inlineStr">
         <is>
           <t>Modala geçerli bir veri girilerek Add to dairy butonu tıklanır</t>
         </is>
       </c>
-      <c r="V34" s="0" t="inlineStr">
-        <is>
-          <t>Beril Ovayurt</t>
-        </is>
-      </c>
-      <c r="W34" s="0" t="inlineStr">
+      <c r="V40" s="0" t="inlineStr">
+        <is>
+          <t>Beril Ovayurt</t>
+        </is>
+      </c>
+      <c r="W40" s="0" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="X34" s="0" t="inlineStr">
+      <c r="X40" s="0" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
     </row>
-    <row r="35" spans="1:24" customHeight="0">
-      <c r="P35" s="34" t="inlineStr">
+    <row r="41" spans="1:24" customHeight="0">
+      <c r="P41" s="40" t="inlineStr">
         <is>
           <t>
 Step Description:
@@ -2058,79 +2351,79 @@
 &lt;p&gt;Eklenen ürünün tüketilenler listesinde bulunduğu gözlenir&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="S35" s="0" t="inlineStr">
+      <c r="S41" s="0" t="inlineStr">
         <is>
           <t>&lt;p&gt;Eklenen ürünün tüketilenler listesinde bulunduğu gözlenir&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="T35" s="0" t="inlineStr">
-        <is>
-          <t>Passed</t>
-        </is>
-      </c>
-      <c r="U35" s="0" t="inlineStr">
+      <c r="T41" s="0" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="U41" s="0" t="inlineStr">
         <is>
           <t>&lt;p&gt;Tüketilenler listesi açılır&lt;/p&gt;</t>
         </is>
       </c>
     </row>
-    <row r="36" spans="1:24" customHeight="0">
-      <c r="A36" s="0" t="inlineStr">
+    <row r="42" spans="1:24" customHeight="0">
+      <c r="A42" s="0" t="inlineStr">
         <is>
           <t>T151</t>
         </is>
       </c>
-      <c r="B36" s="0" t="inlineStr">
+      <c r="B42" s="0" t="inlineStr">
         <is>
           <t>TC - 032 [AU - PR] - Next product butonu davranışı</t>
         </is>
       </c>
-      <c r="C36" s="0" t="inlineStr">
-        <is>
-          <t>Beril Ovayurt</t>
-        </is>
-      </c>
-      <c r="D36" s="0" t="inlineStr">
-        <is>
-          <t>Beril Ovayurt</t>
-        </is>
-      </c>
-      <c r="E36" s="0" t="inlineStr">
+      <c r="C42" s="0" t="inlineStr">
+        <is>
+          <t>Beril Ovayurt</t>
+        </is>
+      </c>
+      <c r="D42" s="0" t="inlineStr">
+        <is>
+          <t>Beril Ovayurt</t>
+        </is>
+      </c>
+      <c r="E42" s="0" t="inlineStr">
         <is>
           <t>C87</t>
         </is>
       </c>
-      <c r="F36" s="0" t="inlineStr">
+      <c r="F42" s="0" t="inlineStr">
         <is>
           <t>&lt;p margin-left:0cm;"" data-pasted=""true""&gt;Sonuç: Passed&lt;/p&gt;&lt;p margin-left:0cm;""&gt;&lt;br&gt;&lt;/p&gt;&lt;p margin-left:0cm;""&gt;Beklenen sonuç elde edildi.&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="I36" s="0" t="inlineStr">
+      <c r="I42" s="0" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="J36" s="0" t="inlineStr">
+      <c r="J42" s="0" t="inlineStr">
         <is>
           <t>Sprint 6 - AU - PR Test Çalıştırması</t>
         </is>
       </c>
-      <c r="L36" s="0" t="inlineStr">
+      <c r="L42" s="0" t="inlineStr">
         <is>
           <t>R17</t>
         </is>
       </c>
-      <c r="M36" s="0" t="inlineStr">
+      <c r="M42" s="0" t="inlineStr">
         <is>
           <t>06 - Yetkili Kullanıcı - Products (AU - PR)</t>
         </is>
       </c>
-      <c r="N36" s="0" t="inlineStr">
-        <is>
-          <t>Passed</t>
-        </is>
-      </c>
-      <c r="P36" s="35" t="inlineStr">
+      <c r="N42" s="0" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="P42" s="41" t="inlineStr">
         <is>
           <t>Step Description:
 Next Product butonuna tıklanır
@@ -2138,94 +2431,94 @@
 Modal kapanır ve product sayfasında kalınır</t>
         </is>
       </c>
-      <c r="S36" s="0" t="inlineStr">
+      <c r="S42" s="0" t="inlineStr">
         <is>
           <t>Modal kapanır ve product sayfasında kalınır</t>
         </is>
       </c>
-      <c r="T36" s="0" t="inlineStr">
-        <is>
-          <t>Passed</t>
-        </is>
-      </c>
-      <c r="U36" s="0" t="inlineStr">
+      <c r="T42" s="0" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="U42" s="0" t="inlineStr">
         <is>
           <t>Next Product butonuna tıklanır</t>
         </is>
       </c>
-      <c r="V36" s="0" t="inlineStr">
-        <is>
-          <t>Beril Ovayurt</t>
-        </is>
-      </c>
-      <c r="W36" s="0" t="inlineStr">
+      <c r="V42" s="0" t="inlineStr">
+        <is>
+          <t>Beril Ovayurt</t>
+        </is>
+      </c>
+      <c r="W42" s="0" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="X36" s="0" t="inlineStr">
+      <c r="X42" s="0" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
     </row>
-    <row r="37" spans="1:24" customHeight="0">
-      <c r="A37" s="0" t="inlineStr">
+    <row r="43" spans="1:24" customHeight="0">
+      <c r="A43" s="0" t="inlineStr">
         <is>
           <t>T152</t>
         </is>
       </c>
-      <c r="B37" s="0" t="inlineStr">
+      <c r="B43" s="0" t="inlineStr">
         <is>
           <t>TC - 033 [AU - PR] - To the diary bağlantısı davranışı</t>
         </is>
       </c>
-      <c r="C37" s="0" t="inlineStr">
-        <is>
-          <t>Beril Ovayurt</t>
-        </is>
-      </c>
-      <c r="D37" s="0" t="inlineStr">
-        <is>
-          <t>Beril Ovayurt</t>
-        </is>
-      </c>
-      <c r="E37" s="0" t="inlineStr">
+      <c r="C43" s="0" t="inlineStr">
+        <is>
+          <t>Beril Ovayurt</t>
+        </is>
+      </c>
+      <c r="D43" s="0" t="inlineStr">
+        <is>
+          <t>Beril Ovayurt</t>
+        </is>
+      </c>
+      <c r="E43" s="0" t="inlineStr">
         <is>
           <t>C88</t>
         </is>
       </c>
-      <c r="F37" s="0" t="inlineStr">
+      <c r="F43" s="0" t="inlineStr">
         <is>
           <t>&lt;p margin-left:0cm;"" data-pasted=""true""&gt;Sonuç: Passed&lt;/p&gt;&lt;p margin-left:0cm;""&gt;&lt;br&gt;&lt;/p&gt;&lt;p margin-left:0cm;""&gt;Beklenen sonuç elde edildi.&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="I37" s="0" t="inlineStr">
+      <c r="I43" s="0" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="J37" s="0" t="inlineStr">
+      <c r="J43" s="0" t="inlineStr">
         <is>
           <t>Sprint 6 - AU - PR Test Çalıştırması</t>
         </is>
       </c>
-      <c r="L37" s="0" t="inlineStr">
+      <c r="L43" s="0" t="inlineStr">
         <is>
           <t>R17</t>
         </is>
       </c>
-      <c r="M37" s="0" t="inlineStr">
+      <c r="M43" s="0" t="inlineStr">
         <is>
           <t>06 - Yetkili Kullanıcı - Products (AU - PR)</t>
         </is>
       </c>
-      <c r="N37" s="0" t="inlineStr">
-        <is>
-          <t>Passed</t>
-        </is>
-      </c>
-      <c r="P37" s="36" t="inlineStr">
+      <c r="N43" s="0" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="P43" s="42" t="inlineStr">
         <is>
           <t>Step Description:
 To the diary bağlantısı tıklanır
@@ -2233,94 +2526,94 @@
 Kullanıcı Diary sayfasına yönlendirilir</t>
         </is>
       </c>
-      <c r="S37" s="0" t="inlineStr">
+      <c r="S43" s="0" t="inlineStr">
         <is>
           <t>Kullanıcı Diary sayfasına yönlendirilir</t>
         </is>
       </c>
-      <c r="T37" s="0" t="inlineStr">
-        <is>
-          <t>Passed</t>
-        </is>
-      </c>
-      <c r="U37" s="0" t="inlineStr">
+      <c r="T43" s="0" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="U43" s="0" t="inlineStr">
         <is>
           <t>To the diary bağlantısı tıklanır</t>
         </is>
       </c>
-      <c r="V37" s="0" t="inlineStr">
-        <is>
-          <t>Beril Ovayurt</t>
-        </is>
-      </c>
-      <c r="W37" s="0" t="inlineStr">
+      <c r="V43" s="0" t="inlineStr">
+        <is>
+          <t>Beril Ovayurt</t>
+        </is>
+      </c>
+      <c r="W43" s="0" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="X37" s="0" t="inlineStr">
+      <c r="X43" s="0" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
     </row>
-    <row r="38" spans="1:24" customHeight="0">
-      <c r="A38" s="0" t="inlineStr">
+    <row r="44" spans="1:24" customHeight="0">
+      <c r="A44" s="0" t="inlineStr">
         <is>
           <t>T153</t>
         </is>
       </c>
-      <c r="B38" s="0" t="inlineStr">
+      <c r="B44" s="0" t="inlineStr">
         <is>
           <t>TC - 034 [AU - PR] - Modal Pencerede Çarpı işareti (X) davranışı</t>
         </is>
       </c>
-      <c r="C38" s="0" t="inlineStr">
-        <is>
-          <t>Beril Ovayurt</t>
-        </is>
-      </c>
-      <c r="D38" s="0" t="inlineStr">
-        <is>
-          <t>Beril Ovayurt</t>
-        </is>
-      </c>
-      <c r="E38" s="0" t="inlineStr">
+      <c r="C44" s="0" t="inlineStr">
+        <is>
+          <t>Beril Ovayurt</t>
+        </is>
+      </c>
+      <c r="D44" s="0" t="inlineStr">
+        <is>
+          <t>Beril Ovayurt</t>
+        </is>
+      </c>
+      <c r="E44" s="0" t="inlineStr">
         <is>
           <t>C89</t>
         </is>
       </c>
-      <c r="F38" s="0" t="inlineStr">
+      <c r="F44" s="0" t="inlineStr">
         <is>
           <t>&lt;p margin-left:0cm;"" data-pasted=""true""&gt;Sonuç: Passed&lt;/p&gt;&lt;p margin-left:0cm;""&gt;&lt;br&gt;&lt;/p&gt;&lt;p margin-left:0cm;""&gt;Beklenen sonuç elde edildi.&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="I38" s="0" t="inlineStr">
+      <c r="I44" s="0" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="J38" s="0" t="inlineStr">
+      <c r="J44" s="0" t="inlineStr">
         <is>
           <t>Sprint 6 - AU - PR Test Çalıştırması</t>
         </is>
       </c>
-      <c r="L38" s="0" t="inlineStr">
+      <c r="L44" s="0" t="inlineStr">
         <is>
           <t>R17</t>
         </is>
       </c>
-      <c r="M38" s="0" t="inlineStr">
+      <c r="M44" s="0" t="inlineStr">
         <is>
           <t>06 - Yetkili Kullanıcı - Products (AU - PR)</t>
         </is>
       </c>
-      <c r="N38" s="0" t="inlineStr">
-        <is>
-          <t>Passed</t>
-        </is>
-      </c>
-      <c r="P38" s="37" t="inlineStr">
+      <c r="N44" s="0" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="P44" s="43" t="inlineStr">
         <is>
           <t>Step Description:
 Çarpı simgesi (X) tıklanır
@@ -2328,32 +2621,32 @@
 Modal kapanır ve kullanıcı mevcut sayfada kalır</t>
         </is>
       </c>
-      <c r="S38" s="0" t="inlineStr">
+      <c r="S44" s="0" t="inlineStr">
         <is>
           <t>Modal kapanır ve kullanıcı mevcut sayfada kalır</t>
         </is>
       </c>
-      <c r="T38" s="0" t="inlineStr">
-        <is>
-          <t>Passed</t>
-        </is>
-      </c>
-      <c r="U38" s="0" t="inlineStr">
+      <c r="T44" s="0" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="U44" s="0" t="inlineStr">
         <is>
           <t>Çarpı simgesi (X) tıklanır</t>
         </is>
       </c>
-      <c r="V38" s="0" t="inlineStr">
-        <is>
-          <t>Beril Ovayurt</t>
-        </is>
-      </c>
-      <c r="W38" s="0" t="inlineStr">
+      <c r="V44" s="0" t="inlineStr">
+        <is>
+          <t>Beril Ovayurt</t>
+        </is>
+      </c>
+      <c r="W44" s="0" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="X38" s="0" t="inlineStr">
+      <c r="X44" s="0" t="inlineStr">
         <is>
           <t>00</t>
         </is>
